--- a/2022/South2/South2_members_final.xlsx
+++ b/2022/South2/South2_members_final.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
